--- a/docs/PREP_MAKLO_3Numeros.xlsx
+++ b/docs/PREP_MAKLO_3Numeros.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costo de servir" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los 3 numeros" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ancla de valor (mesa)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenario agencia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -166,11 +167,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +259,25 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1757,8 +1821,8 @@
           <t>Regla escrita §2 del PREP. Mesas separadas, sin excepcion. 🔴</t>
         </is>
       </c>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="38" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
@@ -1771,8 +1835,8 @@
           <t>Nos vuelve el intermediario que ELLOS decidieron eliminar. 🔴</t>
         </is>
       </c>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="34" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="38" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="22" t="inlineStr">
@@ -1785,8 +1849,8 @@
           <t>Rompe la neutralidad = rompe el activo. 🔴</t>
         </is>
       </c>
-      <c r="D23" s="34" t="n"/>
-      <c r="E23" s="34" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="38" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="22" t="inlineStr">
@@ -1799,8 +1863,8 @@
           <t>Regla de mesa #3: sin presupuesto de demanda no hay mandato. 🔴</t>
         </is>
       </c>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2007,4 +2071,451 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>¿ENTRA UNA AGENCIA DE MEDIOS? — las 3 estructuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta Algoritmo Studio (jul-2026): USD 2.250/mes, minimo 6 meses, NO incluye pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Regla: el compromiso de 6 meses lo asume QUIEN TIENE EL PROYECTO, nunca quien lo sirve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>INPUTS DE ESTA HOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Costo mensual de la agencia</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>De la propuesta: USD 2.250/mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Meses de compromiso minimo</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Contratacion minima exigida por la agencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Horas/mes de coordinacion con la agencia</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Si la agencia opera, vos coordinas (no ejecutas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Presupuesto de pauta mensual de MAKLO</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LLENAR EN LA MESA (pregunta obligatoria #2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>LAS 3 ESTRUCTURAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>A · Contexto opera</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>B · Contexto subcontrata</t>
+        </is>
+      </c>
+      <c r="E14" s="42" t="inlineStr">
+        <is>
+          <t>C · MAKLO contrata directo</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Costo mensual de Contexto</t>
+        </is>
+      </c>
+      <c r="C15" s="14">
+        <f>'Costo de servir'!C22</f>
+        <v/>
+      </c>
+      <c r="D15" s="14">
+        <f>'Costo de servir'!C22+'Escenario agencia'!C7</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>'Costo de servir'!C22-Supuestos!C23*Supuestos!C7+'Escenario agencia'!C9*Supuestos!C7</f>
+        <v/>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>En C no ejecutas campana: solo coordinas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cobro mensual a MAKLO (margen target)</t>
+        </is>
+      </c>
+      <c r="C16" s="14">
+        <f>C15*(1+Supuestos!C30)</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>D15*(1+Supuestos!C30)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>E15*(1+Supuestos!C30)</f>
+        <v/>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Lo que Contexto factura, con tu margen objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>+ Agencia (si la paga MAKLO aparte)</t>
+        </is>
+      </c>
+      <c r="C17" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D17" s="14">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>'Escenario agencia'!C7</f>
+        <v/>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>En C la agencia le factura a MAKLO, no a vos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>+ Pauta (siempre la pone MAKLO)</t>
+        </is>
+      </c>
+      <c r="C18" s="14">
+        <f>'Escenario agencia'!C10</f>
+        <v/>
+      </c>
+      <c r="D18" s="14">
+        <f>'Escenario agencia'!C10</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>'Escenario agencia'!C10</f>
+        <v/>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Regla de mesa #3: sin presupuesto de pauta no hay mandato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="43">
+        <f> TOTAL MENSUAL QUE PAGA MAKLO</f>
+        <v/>
+      </c>
+      <c r="C19" s="26">
+        <f>C16+C17+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>D16+D17+D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>E16+E17+E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>EL numero que decide si el proyecto aguanta. Contra su presupuesto sostenible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Margen mensual de Contexto</t>
+        </is>
+      </c>
+      <c r="C20" s="14">
+        <f>C16-C15</f>
+        <v/>
+      </c>
+      <c r="D20" s="14">
+        <f>D16-D15</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>E16-E15</f>
+        <v/>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Lo que te queda despues de costos, por mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>EL RIESGO DEL COMPROMISO DE 6 MESES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>A · Contexto opera</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>B · Contexto subcontrata</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>C · MAKLO contrata directo</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Compromiso total con la agencia</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="45">
+        <f>'Escenario agencia'!C7*'Escenario agencia'!C8</f>
+        <v/>
+      </c>
+      <c r="E24" s="45">
+        <f>'Escenario agencia'!C7*'Escenario agencia'!C8</f>
+        <v/>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>6 meses x costo mensual de la agencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>¿QUIEN lo asume si el mandato se cae?</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>Nadie</t>
+        </is>
+      </c>
+      <c r="D25" s="47" t="inlineStr">
+        <is>
+          <t>CONTEXTO</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>MAKLO</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>En B financias la demanda de un proyecto ajeno — lo que la propuesta §5 prohibe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>OK si te dan las horas</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>RECOMENDADA</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>C mantiene tu fee limpio, te saca el riesgo y te deja duenio del foso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>COMO SE USA EN LA MESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>1. NO llegues con la agencia decidida. Primero escucha el presupuesto sostenible de Jorge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>2. Llena 'Presupuesto de pauta mensual' arriba con lo que el diga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>3. Compara el TOTAL MENSUAL de cada columna contra ese numero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>4. Si no entra la agencia: opera vos la pauta (columna A) — sale mucho mas barato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>5. Si entra: que MAKLO firme DIRECTO con la agencia (columna C). Nunca vos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>